--- a/Excel/CycleConfig.xlsx
+++ b/Excel/CycleConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="UnitProto" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="27">
   <si>
     <t>Id</t>
   </si>
@@ -84,6 +84,9 @@
   </si>
   <si>
     <t>7500,7500,7500,7500,7500,7500,750,360</t>
+  </si>
+  <si>
+    <t>#</t>
   </si>
   <si>
     <t>2001,2002,2003,2004,2005,2006,2010,38,110</t>
@@ -1097,7 +1100,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:G20"/>
+  <dimension ref="A3:G20"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="21.125" style="1" customWidth="1"/>
@@ -1292,7 +1295,13 @@
         <v>18</v>
       </c>
     </row>
-    <row r="16" spans="3:6">
+    <row r="16" spans="1:6">
+      <c r="A16" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>19</v>
+      </c>
       <c r="C16" s="1">
         <v>11</v>
       </c>
@@ -1300,13 +1309,19 @@
         <v>11</v>
       </c>
       <c r="E16" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="F16" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="17" spans="3:6">
+      <c r="B17" s="1" t="s">
+        <v>19</v>
+      </c>
       <c r="C17" s="1">
         <v>12</v>
       </c>
@@ -1314,13 +1329,19 @@
         <v>12</v>
       </c>
       <c r="E17" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="F17" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="18" spans="3:6">
+      <c r="B18" s="1" t="s">
+        <v>19</v>
+      </c>
       <c r="C18" s="1">
         <v>13</v>
       </c>
@@ -1328,13 +1349,19 @@
         <v>13</v>
       </c>
       <c r="E18" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
+      <c r="A19" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="F18" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="19" spans="3:6">
+      <c r="B19" s="1" t="s">
+        <v>19</v>
+      </c>
       <c r="C19" s="1">
         <v>14</v>
       </c>
@@ -1342,13 +1369,19 @@
         <v>14</v>
       </c>
       <c r="E19" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="F19" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="20" spans="3:7">
+      <c r="B20" s="1" t="s">
+        <v>19</v>
+      </c>
       <c r="C20" s="1">
         <v>15</v>
       </c>
@@ -1356,13 +1389,13 @@
         <v>15</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/CycleConfig.xlsx
+++ b/Excel/CycleConfig.xlsx
@@ -27,11 +27,14 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="58">
   <si>
     <t>Id</t>
   </si>
   <si>
+    <t>Type</t>
+  </si>
+  <si>
     <t>Cycle</t>
   </si>
   <si>
@@ -41,73 +44,163 @@
     <t>AttrValueList</t>
   </si>
   <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>RequireLevel</t>
+  </si>
+  <si>
     <t>int</t>
   </si>
   <si>
-    <t>long</t>
-  </si>
-  <si>
     <t>int[]</t>
   </si>
   <si>
     <t>long[]</t>
   </si>
   <si>
+    <t>string</t>
+  </si>
+  <si>
     <t>2001,2002,2003,2004,2005,2006,2010,38</t>
   </si>
   <si>
     <t>300,300,300,300,300,300,30,15</t>
   </si>
   <si>
+    <t>一转</t>
+  </si>
+  <si>
     <t>700,700,700,700,700,700,70,35</t>
   </si>
   <si>
+    <t>二转</t>
+  </si>
+  <si>
     <t>1200,1200,1200,1200,1200,1200,120,60</t>
   </si>
   <si>
+    <t>三转</t>
+  </si>
+  <si>
     <t>1800,1800,1800,1800,1800,1800,180,90</t>
   </si>
   <si>
+    <t>四转</t>
+  </si>
+  <si>
     <t>2500,2500,2500,2500,2500,2500,250,125</t>
   </si>
   <si>
+    <t>五转</t>
+  </si>
+  <si>
     <t>3300,3300,3300,3300,3300,3300,330,165</t>
   </si>
   <si>
+    <t>六转</t>
+  </si>
+  <si>
     <t>4200,4200,4200,4200,4200,4200,420,210</t>
   </si>
   <si>
+    <t>七转</t>
+  </si>
+  <si>
     <t>5200,5200,5200,5200,5200,5200,520,260</t>
   </si>
   <si>
+    <t>八转</t>
+  </si>
+  <si>
     <t>6300,6300,6300,6300,6300,6300,630,310</t>
   </si>
   <si>
+    <t>九转</t>
+  </si>
+  <si>
     <t>7500,7500,7500,7500,7500,7500,750,360</t>
   </si>
   <si>
-    <t>#</t>
-  </si>
-  <si>
-    <t>2001,2002,2003,2004,2005,2006,2010,38,110</t>
-  </si>
-  <si>
-    <t>8800,8800,8800,8800,8800,8800,880,410,10</t>
-  </si>
-  <si>
-    <t>10200,10200,10200,10200,10200,10200,1020,460,20</t>
-  </si>
-  <si>
-    <t>11700,11700,11700,11700,11700,11700,1170,510,30</t>
-  </si>
-  <si>
-    <t>13300,13300,13300,13300,13300,13300,1330,560,40</t>
-  </si>
-  <si>
-    <t>15000,15000,15000,15000,15000,15000,1500,610,50</t>
-  </si>
-  <si>
-    <t>15+18</t>
+    <t>十转</t>
+  </si>
+  <si>
+    <t>2001,2002,2003,2004,2005,2006,2010,110</t>
+  </si>
+  <si>
+    <t>200,200,200,200,200,200,30,10</t>
+  </si>
+  <si>
+    <t>练气一层</t>
+  </si>
+  <si>
+    <t>练气</t>
+  </si>
+  <si>
+    <t>400,600,600,600,600,600,60,20</t>
+  </si>
+  <si>
+    <t>练气二层</t>
+  </si>
+  <si>
+    <t>筑基</t>
+  </si>
+  <si>
+    <t>800,1200,1200,1200,1200,1200,120,30</t>
+  </si>
+  <si>
+    <t>练气三层</t>
+  </si>
+  <si>
+    <t>金丹</t>
+  </si>
+  <si>
+    <t>1600,2400,2400,2400,2400,2400,180,40</t>
+  </si>
+  <si>
+    <t>练气四层</t>
+  </si>
+  <si>
+    <t>元婴</t>
+  </si>
+  <si>
+    <t>3200,3200,3200,3200,3200,3200,320,50</t>
+  </si>
+  <si>
+    <t>练气五层</t>
+  </si>
+  <si>
+    <t>化神</t>
+  </si>
+  <si>
+    <t>练气六层</t>
+  </si>
+  <si>
+    <t>练虚</t>
+  </si>
+  <si>
+    <t>练气七层</t>
+  </si>
+  <si>
+    <t>大乘</t>
+  </si>
+  <si>
+    <t>练气八层</t>
+  </si>
+  <si>
+    <t>合道</t>
+  </si>
+  <si>
+    <t>练气九层</t>
+  </si>
+  <si>
+    <t>渡劫</t>
+  </si>
+  <si>
+    <t>练气十层</t>
+  </si>
+  <si>
+    <t>散仙</t>
   </si>
 </sst>
 </file>
@@ -1100,20 +1193,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:G20"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="6"/>
+  <dimension ref="C3:L25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="1" customWidth="1"/>
     <col min="2" max="2" width="12.75" style="1" customWidth="1"/>
-    <col min="3" max="3" width="8.875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="9.5" style="1" customWidth="1"/>
-    <col min="5" max="5" width="38.75" style="1" customWidth="1"/>
-    <col min="6" max="6" width="41.75" style="1" customWidth="1"/>
-    <col min="7" max="7" width="18.25" style="1" customWidth="1"/>
-    <col min="8" max="16384" width="9" style="1"/>
+    <col min="3" max="4" width="8.875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="9.5" style="1" customWidth="1"/>
+    <col min="6" max="6" width="36.875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="33.625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="9.5" style="1" customWidth="1"/>
+    <col min="9" max="9" width="12.75" style="1" customWidth="1"/>
+    <col min="10" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="3:6">
+    <row r="3" spans="3:9">
       <c r="C3" s="2" t="s">
         <v>0</v>
       </c>
@@ -1126,8 +1220,17 @@
       <c r="F3" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="4" spans="3:6">
+      <c r="G3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="3:9">
       <c r="C4" s="2" t="s">
         <v>0</v>
       </c>
@@ -1140,262 +1243,537 @@
       <c r="F4" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="5" spans="3:6">
+      <c r="G4" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="3:9">
       <c r="C5" s="2" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I5" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="3:6">
+    <row r="6" spans="3:9">
       <c r="C6" s="1">
         <v>1</v>
       </c>
       <c r="D6" s="1">
         <v>1</v>
       </c>
-      <c r="E6" s="3" t="s">
-        <v>8</v>
+      <c r="E6" s="1">
+        <v>1</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="7" spans="3:6">
+        <v>11</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I6" s="1">
+        <v>120000</v>
+      </c>
+    </row>
+    <row r="7" spans="3:9">
       <c r="C7" s="1">
         <v>2</v>
       </c>
       <c r="D7" s="1">
+        <v>1</v>
+      </c>
+      <c r="E7" s="1">
         <v>2</v>
       </c>
-      <c r="E7" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="F7" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="8" spans="3:6">
+        <v>11</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I7" s="1">
+        <v>130000</v>
+      </c>
+    </row>
+    <row r="8" spans="3:9">
       <c r="C8" s="1">
         <v>3</v>
       </c>
       <c r="D8" s="1">
+        <v>1</v>
+      </c>
+      <c r="E8" s="1">
         <v>3</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="F8" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="9" spans="3:6">
+      <c r="G8" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="I8" s="1">
+        <v>140000</v>
+      </c>
+    </row>
+    <row r="9" spans="3:9">
       <c r="C9" s="1">
         <v>4</v>
       </c>
       <c r="D9" s="1">
+        <v>1</v>
+      </c>
+      <c r="E9" s="1">
         <v>4</v>
       </c>
-      <c r="E9" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="F9" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="10" spans="3:6">
+        <v>11</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="I9" s="1">
+        <v>150000</v>
+      </c>
+    </row>
+    <row r="10" spans="3:9">
       <c r="C10" s="1">
         <v>5</v>
       </c>
       <c r="D10" s="1">
+        <v>1</v>
+      </c>
+      <c r="E10" s="1">
         <v>5</v>
       </c>
-      <c r="E10" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="F10" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="11" spans="3:6">
+        <v>11</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I10" s="1">
+        <v>160000</v>
+      </c>
+    </row>
+    <row r="11" spans="3:9">
       <c r="C11" s="1">
         <v>6</v>
       </c>
       <c r="D11" s="1">
+        <v>1</v>
+      </c>
+      <c r="E11" s="1">
         <v>6</v>
       </c>
-      <c r="E11" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="F11" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="12" spans="3:6">
+        <v>11</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I11" s="1">
+        <v>170000</v>
+      </c>
+    </row>
+    <row r="12" spans="3:9">
       <c r="C12" s="1">
         <v>7</v>
       </c>
       <c r="D12" s="1">
+        <v>1</v>
+      </c>
+      <c r="E12" s="1">
         <v>7</v>
       </c>
-      <c r="E12" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="F12" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="13" spans="3:6">
+        <v>11</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="I12" s="1">
+        <v>180000</v>
+      </c>
+    </row>
+    <row r="13" spans="3:9">
       <c r="C13" s="1">
         <v>8</v>
       </c>
       <c r="D13" s="1">
+        <v>1</v>
+      </c>
+      <c r="E13" s="1">
         <v>8</v>
       </c>
-      <c r="E13" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="F13" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="14" spans="3:6">
+        <v>11</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="I13" s="1">
+        <v>190000</v>
+      </c>
+    </row>
+    <row r="14" spans="3:9">
       <c r="C14" s="1">
         <v>9</v>
       </c>
       <c r="D14" s="1">
+        <v>1</v>
+      </c>
+      <c r="E14" s="1">
         <v>9</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="F14" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="15" spans="3:6">
+        <v>11</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I14" s="1">
+        <v>200000</v>
+      </c>
+    </row>
+    <row r="15" spans="3:9">
       <c r="C15" s="1">
         <v>10</v>
       </c>
       <c r="D15" s="1">
+        <v>1</v>
+      </c>
+      <c r="E15" s="1">
         <v>10</v>
       </c>
-      <c r="E15" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="F15" s="3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>19</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="I15" s="1">
+        <v>210000</v>
+      </c>
+    </row>
+    <row r="16" spans="3:12">
       <c r="C16" s="1">
         <v>11</v>
       </c>
       <c r="D16" s="1">
+        <v>2</v>
+      </c>
+      <c r="E16" s="1">
         <v>11</v>
       </c>
-      <c r="E16" s="3" t="s">
-        <v>20</v>
-      </c>
       <c r="F16" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>19</v>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="I16" s="1">
+        <v>211000</v>
+      </c>
+      <c r="J16" s="1"/>
+      <c r="L16" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="17" spans="3:12">
       <c r="C17" s="1">
         <v>12</v>
       </c>
       <c r="D17" s="1">
+        <v>2</v>
+      </c>
+      <c r="E17" s="1">
         <v>12</v>
       </c>
-      <c r="E17" s="3" t="s">
-        <v>20</v>
-      </c>
       <c r="F17" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>19</v>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I17" s="1">
+        <v>212000</v>
+      </c>
+      <c r="J17" s="1"/>
+      <c r="L17" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="18" spans="3:12">
       <c r="C18" s="1">
         <v>13</v>
       </c>
       <c r="D18" s="1">
+        <v>2</v>
+      </c>
+      <c r="E18" s="1">
         <v>13</v>
       </c>
-      <c r="E18" s="3" t="s">
-        <v>20</v>
-      </c>
       <c r="F18" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>19</v>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="I18" s="1">
+        <v>213000</v>
+      </c>
+      <c r="J18" s="1"/>
+      <c r="L18" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="19" spans="3:12">
       <c r="C19" s="1">
         <v>14</v>
       </c>
       <c r="D19" s="1">
+        <v>2</v>
+      </c>
+      <c r="E19" s="1">
         <v>14</v>
       </c>
-      <c r="E19" s="3" t="s">
-        <v>20</v>
-      </c>
       <c r="F19" s="3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>19</v>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="I19" s="1">
+        <v>214000</v>
+      </c>
+      <c r="J19" s="1"/>
+      <c r="L19" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="20" spans="3:12">
       <c r="C20" s="1">
         <v>15</v>
       </c>
       <c r="D20" s="1">
+        <v>2</v>
+      </c>
+      <c r="E20" s="1">
         <v>15</v>
       </c>
-      <c r="E20" s="3" t="s">
+      <c r="F20" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="I20" s="1">
+        <v>215000</v>
+      </c>
+      <c r="J20" s="1"/>
+      <c r="L20" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="21" spans="3:12">
+      <c r="C21" s="1">
+        <v>16</v>
+      </c>
+      <c r="D21" s="1">
+        <v>2</v>
+      </c>
+      <c r="E21" s="1">
+        <v>16</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="I21" s="1">
+        <v>216000</v>
+      </c>
+      <c r="J21" s="1"/>
+      <c r="L21" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="22" spans="3:12">
+      <c r="C22" s="1">
+        <v>17</v>
+      </c>
+      <c r="D22" s="1">
+        <v>2</v>
+      </c>
+      <c r="E22" s="1">
+        <v>17</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="I22" s="1">
+        <v>217000</v>
+      </c>
+      <c r="J22" s="1"/>
+      <c r="L22" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="23" spans="3:12">
+      <c r="C23" s="1">
+        <v>18</v>
+      </c>
+      <c r="D23" s="1">
+        <v>2</v>
+      </c>
+      <c r="E23" s="1">
+        <v>18</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="I23" s="1">
+        <v>218000</v>
+      </c>
+      <c r="J23" s="1"/>
+      <c r="L23" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="24" spans="3:12">
+      <c r="C24" s="1">
+        <v>19</v>
+      </c>
+      <c r="D24" s="1">
+        <v>2</v>
+      </c>
+      <c r="E24" s="1">
+        <v>19</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="I24" s="1">
+        <v>219000</v>
+      </c>
+      <c r="J24" s="1"/>
+      <c r="L24" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="25" spans="3:12">
+      <c r="C25" s="1">
         <v>20</v>
       </c>
-      <c r="F20" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="G20" s="1" t="s">
-        <v>26</v>
+      <c r="D25" s="1">
+        <v>2</v>
+      </c>
+      <c r="E25" s="1">
+        <v>20</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="I25" s="1">
+        <v>220000</v>
+      </c>
+      <c r="J25" s="1"/>
+      <c r="L25" s="1" t="s">
+        <v>57</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/CycleConfig.xlsx
+++ b/Excel/CycleConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="UnitProto" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="59">
+  <si>
+    <t>#</t>
+  </si>
   <si>
     <t>Id</t>
   </si>
@@ -125,58 +128,61 @@
     <t>十转</t>
   </si>
   <si>
-    <t>2001,2002,2003,2004,2005,2006,2010,110</t>
-  </si>
-  <si>
-    <t>200,200,200,200,200,200,30,10</t>
+    <t>2001,2002,2003,2004,2005,2006,2010,31,32,110</t>
+  </si>
+  <si>
+    <t>200,200,200,200,200,200,30,5,2,10</t>
+  </si>
+  <si>
+    <t>练气</t>
   </si>
   <si>
     <t>练气一层</t>
   </si>
   <si>
-    <t>练气</t>
-  </si>
-  <si>
-    <t>400,600,600,600,600,600,60,20</t>
+    <t>400,600,600,600,600,600,60,10,4,20</t>
+  </si>
+  <si>
+    <t>筑基</t>
   </si>
   <si>
     <t>练气二层</t>
   </si>
   <si>
-    <t>筑基</t>
-  </si>
-  <si>
-    <t>800,1200,1200,1200,1200,1200,120,30</t>
+    <t>800,1200,1200,1200,1200,1200,120,15,6,30</t>
+  </si>
+  <si>
+    <t>金丹</t>
   </si>
   <si>
     <t>练气三层</t>
   </si>
   <si>
-    <t>金丹</t>
-  </si>
-  <si>
-    <t>1600,2400,2400,2400,2400,2400,180,40</t>
+    <t>1600,2400,2400,2400,2400,2400,180,20,8,40</t>
+  </si>
+  <si>
+    <t>元婴</t>
   </si>
   <si>
     <t>练气四层</t>
   </si>
   <si>
-    <t>元婴</t>
-  </si>
-  <si>
-    <t>3200,3200,3200,3200,3200,3200,320,50</t>
+    <t>3200,3200,3200,3200,3200,3200,320,5,2,50</t>
+  </si>
+  <si>
+    <t>化神</t>
   </si>
   <si>
     <t>练气五层</t>
   </si>
   <si>
-    <t>化神</t>
+    <t>练虚</t>
   </si>
   <si>
     <t>练气六层</t>
   </si>
   <si>
-    <t>练虚</t>
+    <t>合体</t>
   </si>
   <si>
     <t>练气七层</t>
@@ -188,19 +194,16 @@
     <t>练气八层</t>
   </si>
   <si>
-    <t>合道</t>
+    <t>渡劫</t>
   </si>
   <si>
     <t>练气九层</t>
   </si>
   <si>
-    <t>渡劫</t>
+    <t>散仙</t>
   </si>
   <si>
     <t>练气十层</t>
-  </si>
-  <si>
-    <t>散仙</t>
   </si>
 </sst>
 </file>
@@ -1193,7 +1196,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:L25"/>
+  <dimension ref="C1:J25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="1" customWidth="1"/>
@@ -1201,79 +1204,89 @@
     <col min="3" max="4" width="8.875" style="1" customWidth="1"/>
     <col min="5" max="5" width="9.5" style="1" customWidth="1"/>
     <col min="6" max="6" width="36.875" style="1" customWidth="1"/>
-    <col min="7" max="7" width="33.625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="35.5" style="1" customWidth="1"/>
     <col min="8" max="8" width="9.5" style="1" customWidth="1"/>
     <col min="9" max="9" width="12.75" style="1" customWidth="1"/>
     <col min="10" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
+    <row r="1" spans="10:10">
+      <c r="J1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="10:10">
+      <c r="J2" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
     <row r="3" spans="3:9">
       <c r="C3" s="2" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="3:9">
       <c r="C4" s="2" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="3:9">
       <c r="C5" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="I5" s="2" t="s">
         <v>8</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="6" spans="3:9">
@@ -1281,19 +1294,19 @@
         <v>1</v>
       </c>
       <c r="D6" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6" s="1">
         <v>1</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I6" s="1">
         <v>120000</v>
@@ -1304,19 +1317,19 @@
         <v>2</v>
       </c>
       <c r="D7" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7" s="1">
         <v>2</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I7" s="1">
         <v>130000</v>
@@ -1327,19 +1340,19 @@
         <v>3</v>
       </c>
       <c r="D8" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E8" s="1">
         <v>3</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I8" s="1">
         <v>140000</v>
@@ -1350,19 +1363,19 @@
         <v>4</v>
       </c>
       <c r="D9" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E9" s="1">
         <v>4</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I9" s="1">
         <v>150000</v>
@@ -1373,19 +1386,19 @@
         <v>5</v>
       </c>
       <c r="D10" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E10" s="1">
         <v>5</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I10" s="1">
         <v>160000</v>
@@ -1396,19 +1409,19 @@
         <v>6</v>
       </c>
       <c r="D11" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E11" s="1">
         <v>6</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I11" s="1">
         <v>170000</v>
@@ -1419,19 +1432,19 @@
         <v>7</v>
       </c>
       <c r="D12" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E12" s="1">
         <v>7</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I12" s="1">
         <v>180000</v>
@@ -1442,19 +1455,19 @@
         <v>8</v>
       </c>
       <c r="D13" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E13" s="1">
         <v>8</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I13" s="1">
         <v>190000</v>
@@ -1465,19 +1478,19 @@
         <v>9</v>
       </c>
       <c r="D14" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E14" s="1">
         <v>9</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I14" s="1">
         <v>200000</v>
@@ -1488,292 +1501,282 @@
         <v>10</v>
       </c>
       <c r="D15" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E15" s="1">
         <v>10</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I15" s="1">
         <v>210000</v>
       </c>
     </row>
-    <row r="16" spans="3:12">
+    <row r="16" spans="3:10">
       <c r="C16" s="1">
         <v>11</v>
       </c>
       <c r="D16" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E16" s="1">
         <v>11</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I16" s="1">
         <v>211000</v>
       </c>
-      <c r="J16" s="1"/>
-      <c r="L16" s="1" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="17" spans="3:12">
+      <c r="J16" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="17" spans="3:10">
       <c r="C17" s="1">
         <v>12</v>
       </c>
       <c r="D17" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E17" s="1">
         <v>12</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I17" s="1">
         <v>212000</v>
       </c>
-      <c r="J17" s="1"/>
-      <c r="L17" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="18" spans="3:12">
+      <c r="J17" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="18" spans="3:10">
       <c r="C18" s="1">
         <v>13</v>
       </c>
       <c r="D18" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E18" s="1">
         <v>13</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I18" s="1">
         <v>213000</v>
       </c>
-      <c r="J18" s="1"/>
-      <c r="L18" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="19" spans="3:12">
+      <c r="J18" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="19" spans="3:10">
       <c r="C19" s="1">
         <v>14</v>
       </c>
       <c r="D19" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E19" s="1">
         <v>14</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="I19" s="1">
         <v>214000</v>
       </c>
-      <c r="J19" s="1"/>
-      <c r="L19" s="1" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="20" spans="3:12">
+      <c r="J19" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="20" spans="3:10">
       <c r="C20" s="1">
         <v>15</v>
       </c>
       <c r="D20" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E20" s="1">
         <v>15</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I20" s="1">
         <v>215000</v>
       </c>
-      <c r="J20" s="1"/>
-      <c r="L20" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="21" spans="3:12">
+      <c r="J20" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="21" spans="3:10">
       <c r="C21" s="1">
         <v>16</v>
       </c>
       <c r="D21" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E21" s="1">
         <v>16</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I21" s="1">
         <v>216000</v>
       </c>
-      <c r="J21" s="1"/>
-      <c r="L21" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="22" spans="3:12">
+      <c r="J21" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="22" spans="3:10">
       <c r="C22" s="1">
         <v>17</v>
       </c>
       <c r="D22" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E22" s="1">
         <v>17</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="I22" s="1">
         <v>217000</v>
       </c>
-      <c r="J22" s="1"/>
-      <c r="L22" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="23" spans="3:12">
+      <c r="J22" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="23" spans="3:10">
       <c r="C23" s="1">
         <v>18</v>
       </c>
       <c r="D23" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E23" s="1">
         <v>18</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I23" s="1">
         <v>218000</v>
       </c>
-      <c r="J23" s="1"/>
-      <c r="L23" s="1" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="24" spans="3:12">
+      <c r="J23" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="24" spans="3:10">
       <c r="C24" s="1">
         <v>19</v>
       </c>
       <c r="D24" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E24" s="1">
         <v>19</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I24" s="1">
         <v>219000</v>
       </c>
-      <c r="J24" s="1"/>
-      <c r="L24" s="1" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="25" spans="3:12">
+      <c r="J24" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="25" spans="3:10">
       <c r="C25" s="1">
         <v>20</v>
       </c>
       <c r="D25" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E25" s="1">
         <v>20</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I25" s="1">
         <v>220000</v>
       </c>
-      <c r="J25" s="1"/>
-      <c r="L25" s="1" t="s">
-        <v>57</v>
+      <c r="J25" s="1" t="s">
+        <v>58</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/CycleConfig.xlsx
+++ b/Excel/CycleConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="UnitProto" sheetId="1" r:id="rId1"/>
@@ -27,10 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="59">
-  <si>
-    <t>#</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="25">
   <si>
     <t>Id</t>
   </si>
@@ -47,12 +44,6 @@
     <t>AttrValueList</t>
   </si>
   <si>
-    <t>Name</t>
-  </si>
-  <si>
-    <t>RequireLevel</t>
-  </si>
-  <si>
     <t>int</t>
   </si>
   <si>
@@ -62,148 +53,55 @@
     <t>long[]</t>
   </si>
   <si>
-    <t>string</t>
-  </si>
-  <si>
     <t>2001,2002,2003,2004,2005,2006,2010,38</t>
   </si>
   <si>
     <t>300,300,300,300,300,300,30,15</t>
   </si>
   <si>
-    <t>一转</t>
-  </si>
-  <si>
     <t>700,700,700,700,700,700,70,35</t>
   </si>
   <si>
-    <t>二转</t>
-  </si>
-  <si>
     <t>1200,1200,1200,1200,1200,1200,120,60</t>
   </si>
   <si>
-    <t>三转</t>
-  </si>
-  <si>
     <t>1800,1800,1800,1800,1800,1800,180,90</t>
   </si>
   <si>
-    <t>四转</t>
-  </si>
-  <si>
     <t>2500,2500,2500,2500,2500,2500,250,125</t>
   </si>
   <si>
-    <t>五转</t>
-  </si>
-  <si>
     <t>3300,3300,3300,3300,3300,3300,330,165</t>
   </si>
   <si>
-    <t>六转</t>
-  </si>
-  <si>
     <t>4200,4200,4200,4200,4200,4200,420,210</t>
   </si>
   <si>
-    <t>七转</t>
-  </si>
-  <si>
     <t>5200,5200,5200,5200,5200,5200,520,260</t>
   </si>
   <si>
-    <t>八转</t>
-  </si>
-  <si>
     <t>6300,6300,6300,6300,6300,6300,630,310</t>
   </si>
   <si>
-    <t>九转</t>
-  </si>
-  <si>
     <t>7500,7500,7500,7500,7500,7500,750,360</t>
   </si>
   <si>
-    <t>十转</t>
-  </si>
-  <si>
     <t>2001,2002,2003,2004,2005,2006,2010,31,32,110</t>
   </si>
   <si>
-    <t>200,200,200,200,200,200,30,5,2,10</t>
-  </si>
-  <si>
-    <t>练气</t>
-  </si>
-  <si>
-    <t>练气一层</t>
-  </si>
-  <si>
-    <t>400,600,600,600,600,600,60,10,4,20</t>
-  </si>
-  <si>
-    <t>筑基</t>
-  </si>
-  <si>
-    <t>练气二层</t>
-  </si>
-  <si>
-    <t>800,1200,1200,1200,1200,1200,120,15,6,30</t>
-  </si>
-  <si>
-    <t>金丹</t>
-  </si>
-  <si>
-    <t>练气三层</t>
-  </si>
-  <si>
-    <t>1600,2400,2400,2400,2400,2400,180,20,8,40</t>
-  </si>
-  <si>
-    <t>元婴</t>
-  </si>
-  <si>
-    <t>练气四层</t>
-  </si>
-  <si>
-    <t>3200,3200,3200,3200,3200,3200,320,5,2,50</t>
-  </si>
-  <si>
-    <t>化神</t>
-  </si>
-  <si>
-    <t>练气五层</t>
-  </si>
-  <si>
-    <t>练虚</t>
-  </si>
-  <si>
-    <t>练气六层</t>
-  </si>
-  <si>
-    <t>合体</t>
-  </si>
-  <si>
-    <t>练气七层</t>
-  </si>
-  <si>
-    <t>大乘</t>
-  </si>
-  <si>
-    <t>练气八层</t>
-  </si>
-  <si>
-    <t>渡劫</t>
-  </si>
-  <si>
-    <t>练气九层</t>
-  </si>
-  <si>
-    <t>散仙</t>
-  </si>
-  <si>
-    <t>练气十层</t>
+    <t>400,400,150,150,150,150,30,5,2,10</t>
+  </si>
+  <si>
+    <t>800,800,300,300,300,300,60,10,4,20</t>
+  </si>
+  <si>
+    <t>1600,1600,600,600,600,600,120,15,6,30</t>
+  </si>
+  <si>
+    <t>3200,3200,900,900,900,900,180,20,8,40</t>
+  </si>
+  <si>
+    <t>6400,6400,1500,1500,1500,1500,320,5,2,50</t>
   </si>
 </sst>
 </file>
@@ -1196,8 +1094,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:J25"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <dimension ref="C3:G25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="21.125" style="1" customWidth="1"/>
     <col min="2" max="2" width="12.75" style="1" customWidth="1"/>
@@ -1205,91 +1103,61 @@
     <col min="5" max="5" width="9.5" style="1" customWidth="1"/>
     <col min="6" max="6" width="36.875" style="1" customWidth="1"/>
     <col min="7" max="7" width="35.5" style="1" customWidth="1"/>
-    <col min="8" max="8" width="9.5" style="1" customWidth="1"/>
-    <col min="9" max="9" width="12.75" style="1" customWidth="1"/>
-    <col min="10" max="16384" width="9" style="1"/>
+    <col min="8" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="10:10">
-      <c r="J1" s="1" t="s">
+    <row r="3" spans="3:7">
+      <c r="C3" s="2" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="10:10">
-      <c r="J2" s="1" t="s">
+      <c r="D3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="3:7">
+      <c r="C4" s="2" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="3:9">
-      <c r="C3" s="2" t="s">
+      <c r="D4" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="E4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="F4" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="G4" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="2" t="s">
+    </row>
+    <row r="5" spans="3:7">
+      <c r="C5" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="D5" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="G5" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="3:9">
-      <c r="C4" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" spans="3:9">
-      <c r="C5" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="6" spans="3:9">
+    <row r="6" spans="3:7">
       <c r="C6" s="1">
         <v>1</v>
       </c>
@@ -1300,19 +1168,13 @@
         <v>1</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="I6" s="1">
-        <v>120000</v>
-      </c>
-    </row>
-    <row r="7" spans="3:9">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="3:7">
       <c r="C7" s="1">
         <v>2</v>
       </c>
@@ -1323,19 +1185,13 @@
         <v>2</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="I7" s="1">
-        <v>130000</v>
-      </c>
-    </row>
-    <row r="8" spans="3:9">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="3:7">
       <c r="C8" s="1">
         <v>3</v>
       </c>
@@ -1346,19 +1202,13 @@
         <v>3</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="I8" s="1">
-        <v>140000</v>
-      </c>
-    </row>
-    <row r="9" spans="3:9">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="3:7">
       <c r="C9" s="1">
         <v>4</v>
       </c>
@@ -1369,19 +1219,13 @@
         <v>4</v>
       </c>
       <c r="F9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G9" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G9" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H9" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="I9" s="1">
-        <v>150000</v>
-      </c>
-    </row>
-    <row r="10" spans="3:9">
+    </row>
+    <row r="10" spans="3:7">
       <c r="C10" s="1">
         <v>5</v>
       </c>
@@ -1392,19 +1236,13 @@
         <v>5</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H10" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="I10" s="1">
-        <v>160000</v>
-      </c>
-    </row>
-    <row r="11" spans="3:9">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" spans="3:7">
       <c r="C11" s="1">
         <v>6</v>
       </c>
@@ -1415,19 +1253,13 @@
         <v>6</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H11" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="I11" s="1">
-        <v>170000</v>
-      </c>
-    </row>
-    <row r="12" spans="3:9">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12" spans="3:7">
       <c r="C12" s="1">
         <v>7</v>
       </c>
@@ -1438,19 +1270,13 @@
         <v>7</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="H12" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="I12" s="1">
-        <v>180000</v>
-      </c>
-    </row>
-    <row r="13" spans="3:9">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13" spans="3:7">
       <c r="C13" s="1">
         <v>8</v>
       </c>
@@ -1461,19 +1287,13 @@
         <v>8</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="H13" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="I13" s="1">
-        <v>190000</v>
-      </c>
-    </row>
-    <row r="14" spans="3:9">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="14" spans="3:7">
       <c r="C14" s="1">
         <v>9</v>
       </c>
@@ -1484,19 +1304,13 @@
         <v>9</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="H14" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="I14" s="1">
-        <v>200000</v>
-      </c>
-    </row>
-    <row r="15" spans="3:9">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="15" spans="3:7">
       <c r="C15" s="1">
         <v>10</v>
       </c>
@@ -1507,19 +1321,13 @@
         <v>10</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="H15" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I15" s="1">
-        <v>210000</v>
-      </c>
-    </row>
-    <row r="16" spans="3:10">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="16" spans="3:7">
       <c r="C16" s="1">
         <v>11</v>
       </c>
@@ -1530,22 +1338,13 @@
         <v>11</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="H16" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="I16" s="1">
-        <v>211000</v>
-      </c>
-      <c r="J16" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="17" spans="3:10">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="17" spans="3:7">
       <c r="C17" s="1">
         <v>12</v>
       </c>
@@ -1556,22 +1355,13 @@
         <v>12</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="H17" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="I17" s="1">
-        <v>212000</v>
-      </c>
-      <c r="J17" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="18" spans="3:10">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="18" spans="3:7">
       <c r="C18" s="1">
         <v>13</v>
       </c>
@@ -1582,22 +1372,13 @@
         <v>13</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="H18" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="I18" s="1">
-        <v>213000</v>
-      </c>
-      <c r="J18" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="19" spans="3:10">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="19" spans="3:7">
       <c r="C19" s="1">
         <v>14</v>
       </c>
@@ -1608,22 +1389,13 @@
         <v>14</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="H19" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="I19" s="1">
-        <v>214000</v>
-      </c>
-      <c r="J19" s="1" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="20" spans="3:10">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="20" spans="3:7">
       <c r="C20" s="1">
         <v>15</v>
       </c>
@@ -1634,22 +1406,13 @@
         <v>15</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="H20" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="I20" s="1">
-        <v>215000</v>
-      </c>
-      <c r="J20" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="21" spans="3:10">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="21" spans="3:7">
       <c r="C21" s="1">
         <v>16</v>
       </c>
@@ -1660,22 +1423,13 @@
         <v>16</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="H21" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="I21" s="1">
-        <v>216000</v>
-      </c>
-      <c r="J21" s="1" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="22" spans="3:10">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="22" spans="3:7">
       <c r="C22" s="1">
         <v>17</v>
       </c>
@@ -1686,22 +1440,13 @@
         <v>17</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="H22" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="I22" s="1">
-        <v>217000</v>
-      </c>
-      <c r="J22" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="23" spans="3:10">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="23" spans="3:7">
       <c r="C23" s="1">
         <v>18</v>
       </c>
@@ -1712,22 +1457,13 @@
         <v>18</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="H23" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="I23" s="1">
-        <v>218000</v>
-      </c>
-      <c r="J23" s="1" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="24" spans="3:10">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="24" spans="3:7">
       <c r="C24" s="1">
         <v>19</v>
       </c>
@@ -1738,22 +1474,13 @@
         <v>19</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="H24" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="I24" s="1">
-        <v>219000</v>
-      </c>
-      <c r="J24" s="1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="25" spans="3:10">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="25" spans="3:7">
       <c r="C25" s="1">
         <v>20</v>
       </c>
@@ -1764,19 +1491,10 @@
         <v>20</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="H25" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="I25" s="1">
-        <v>220000</v>
-      </c>
-      <c r="J25" s="1" t="s">
-        <v>58</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/CycleConfig.xlsx
+++ b/Excel/CycleConfig.xlsx
@@ -89,19 +89,19 @@
     <t>2001,2002,2003,2004,2005,2006,2010,31,32,110</t>
   </si>
   <si>
-    <t>400,400,150,150,150,150,30,5,2,10</t>
-  </si>
-  <si>
-    <t>800,800,300,300,300,300,60,10,4,20</t>
-  </si>
-  <si>
-    <t>1600,1600,600,600,600,600,120,15,6,30</t>
-  </si>
-  <si>
-    <t>3200,3200,900,900,900,900,180,20,8,40</t>
-  </si>
-  <si>
-    <t>6400,6400,1500,1500,1500,1500,320,5,2,50</t>
+    <t>400,400,150,150,150,150,30,5,2,30</t>
+  </si>
+  <si>
+    <t>800,800,300,300,300,300,60,10,4,40</t>
+  </si>
+  <si>
+    <t>1600,1600,600,600,600,600,120,15,6,50</t>
+  </si>
+  <si>
+    <t>3200,3200,900,900,900,900,180,20,8,60</t>
+  </si>
+  <si>
+    <t>6400,6400,1500,1500,1500,1500,320,5,2,70</t>
   </si>
 </sst>
 </file>
@@ -1101,7 +1101,7 @@
     <col min="2" max="2" width="12.75" style="1" customWidth="1"/>
     <col min="3" max="4" width="8.875" style="1" customWidth="1"/>
     <col min="5" max="5" width="9.5" style="1" customWidth="1"/>
-    <col min="6" max="6" width="36.875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="40.75" style="1" customWidth="1"/>
     <col min="7" max="7" width="35.5" style="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="1"/>
   </cols>

--- a/Excel/CycleConfig.xlsx
+++ b/Excel/CycleConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="UnitProto" sheetId="1" r:id="rId1"/>
@@ -86,22 +86,22 @@
     <t>7500,7500,7500,7500,7500,7500,750,360</t>
   </si>
   <si>
-    <t>2001,2002,2003,2004,2005,2006,2010,31,32,110</t>
-  </si>
-  <si>
-    <t>400,400,150,150,150,150,30,5,2,30</t>
-  </si>
-  <si>
-    <t>800,800,300,300,300,300,60,10,4,40</t>
-  </si>
-  <si>
-    <t>1600,1600,600,600,600,600,120,15,6,50</t>
-  </si>
-  <si>
-    <t>3200,3200,900,900,900,900,180,20,8,60</t>
-  </si>
-  <si>
-    <t>6400,6400,1500,1500,1500,1500,320,5,2,70</t>
+    <t>2001,2002,2003,2004,2005,2006,2010,31,32,110,50,51</t>
+  </si>
+  <si>
+    <t>400,400,150,150,150,150,30,5,2,30,3,3</t>
+  </si>
+  <si>
+    <t>800,800,300,300,300,300,60,10,4,40,6,6</t>
+  </si>
+  <si>
+    <t>1600,1600,600,600,600,600,120,15,6,50,9,9</t>
+  </si>
+  <si>
+    <t>3200,3200,900,900,900,900,180,20,8,60,12,12</t>
+  </si>
+  <si>
+    <t>6400,6400,1200,1200,1200,1200,240,25,10,70,15,15</t>
   </si>
 </sst>
 </file>
@@ -1101,8 +1101,8 @@
     <col min="2" max="2" width="12.75" style="1" customWidth="1"/>
     <col min="3" max="4" width="8.875" style="1" customWidth="1"/>
     <col min="5" max="5" width="9.5" style="1" customWidth="1"/>
-    <col min="6" max="6" width="40.75" style="1" customWidth="1"/>
-    <col min="7" max="7" width="35.5" style="1" customWidth="1"/>
+    <col min="6" max="6" width="48.875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="40.75" style="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>

--- a/Excel/CycleConfig.xlsx
+++ b/Excel/CycleConfig.xlsx
@@ -98,7 +98,7 @@
     <t>1600,1600,600,600,600,600,120,15,6,50,9,9</t>
   </si>
   <si>
-    <t>3200,3200,900,900,900,900,180,20,8,60,12,12</t>
+    <t>2400,3200,1200,900,900,900,180,20,8,60,12,12</t>
   </si>
   <si>
     <t>6400,6400,1200,1200,1200,1200,240,25,10,70,15,15</t>

--- a/Excel/CycleConfig.xlsx
+++ b/Excel/CycleConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="30">
   <si>
     <t>Id</t>
   </si>
@@ -101,7 +101,22 @@
     <t>2400,3200,1200,900,900,900,180,20,8,60,12,12</t>
   </si>
   <si>
-    <t>6400,6400,1200,1200,1200,1200,240,25,10,70,15,15</t>
+    <t>3600,6400,1800,1200,1200,1200,240,25,10,70,15,15</t>
+  </si>
+  <si>
+    <t>5400,12800,2400,1800,1800,1800,300,30,12,80,18,18</t>
+  </si>
+  <si>
+    <t>7200,25600,3600,2400,2400,2400,360,35,14,90,21,21</t>
+  </si>
+  <si>
+    <t>9000,51200,4800,3600,3600,3600,420,40,16,100,24,24</t>
+  </si>
+  <si>
+    <t>15000,102400,6000,4800,4800,4800,480,45,18,110,27,27</t>
+  </si>
+  <si>
+    <t>24000,204800,7200,6000,6000,6000,540,50,20,120,30,30</t>
   </si>
 </sst>
 </file>
@@ -1426,7 +1441,7 @@
         <v>19</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="22" spans="3:7">
@@ -1443,7 +1458,7 @@
         <v>19</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="23" spans="3:7">
@@ -1460,7 +1475,7 @@
         <v>19</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="24" spans="3:7">
@@ -1477,7 +1492,7 @@
         <v>19</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="25" spans="3:7">
@@ -1494,7 +1509,7 @@
         <v>19</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/CycleConfig.xlsx
+++ b/Excel/CycleConfig.xlsx
@@ -101,22 +101,22 @@
     <t>2400,3200,1200,900,900,900,180,20,8,60,12,12</t>
   </si>
   <si>
-    <t>3600,6400,1800,1200,1200,1200,240,25,10,70,15,15</t>
-  </si>
-  <si>
-    <t>5400,12800,2400,1800,1800,1800,300,30,12,80,18,18</t>
-  </si>
-  <si>
-    <t>7200,25600,3600,2400,2400,2400,360,35,14,90,21,21</t>
-  </si>
-  <si>
-    <t>9000,51200,4800,3600,3600,3600,420,40,16,100,24,24</t>
-  </si>
-  <si>
-    <t>15000,102400,6000,4800,4800,4800,480,45,18,110,27,27</t>
-  </si>
-  <si>
-    <t>24000,204800,7200,6000,6000,6000,540,50,20,120,30,30</t>
+    <t>3600,6400,2400,1200,1200,1200,240,25,10,70,15,15</t>
+  </si>
+  <si>
+    <t>5400,12800,4800,1800,1800,1800,300,30,12,80,18,18</t>
+  </si>
+  <si>
+    <t>7200,25600,9600,2400,2400,2400,360,35,14,90,21,21</t>
+  </si>
+  <si>
+    <t>9000,51200,19200,3600,3600,3600,420,40,16,100,24,24</t>
+  </si>
+  <si>
+    <t>15000,102400,38400,4800,4800,4800,480,45,18,110,27,27</t>
+  </si>
+  <si>
+    <t>24000,204800,76800,6000,6000,6000,540,50,20,120,30,30</t>
   </si>
 </sst>
 </file>

--- a/Excel/CycleConfig.xlsx
+++ b/Excel/CycleConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="27952" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="UnitProto" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="41">
   <si>
     <t>Id</t>
   </si>
@@ -117,6 +117,39 @@
   </si>
   <si>
     <t>24000,204800,76800,6000,6000,6000,540,50,20,120,30,30</t>
+  </si>
+  <si>
+    <t>2001,2002,2003,2012,31,32,50,51,54,55,108,109</t>
+  </si>
+  <si>
+    <t>100,200,300,100,6,3,3,3,5,5,5,5</t>
+  </si>
+  <si>
+    <t>200,400,600,200,12,6,6,6,10,10,10,10</t>
+  </si>
+  <si>
+    <t>400,800,1200,400,18,9,9,9,15,15,15,15</t>
+  </si>
+  <si>
+    <t>800,1600,2400,800,24,12,12,12,20,20,20,20</t>
+  </si>
+  <si>
+    <t>1600,3200,4800,1600,30,15,15,15,25,25,25,25</t>
+  </si>
+  <si>
+    <t>3200,6400,9600,3200,36,18,18,18,30,30,30,30</t>
+  </si>
+  <si>
+    <t>6400,12800,19200,6400,42,21,21,21,35,35,35,35</t>
+  </si>
+  <si>
+    <t>12800,25600,38400,12800,48,24,24,24,40,40,40,40</t>
+  </si>
+  <si>
+    <t>25600,51200,76800,25600,54,27,27,27,45,45,45,45</t>
+  </si>
+  <si>
+    <t>51200,102400,153600,51200,60,30,30,30,50,50,50,50</t>
   </si>
 </sst>
 </file>
@@ -1109,15 +1142,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:G25"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="6"/>
+  <dimension ref="C3:G37"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.35" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="21.125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="12.75" style="1" customWidth="1"/>
-    <col min="3" max="4" width="8.875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="9.5" style="1" customWidth="1"/>
-    <col min="6" max="6" width="48.875" style="1" customWidth="1"/>
-    <col min="7" max="7" width="40.75" style="1" customWidth="1"/>
+    <col min="1" max="1" width="21.1238938053097" style="1" customWidth="1"/>
+    <col min="2" max="2" width="12.7522123893805" style="1" customWidth="1"/>
+    <col min="3" max="4" width="8.87610619469027" style="1" customWidth="1"/>
+    <col min="5" max="5" width="9.50442477876106" style="1" customWidth="1"/>
+    <col min="6" max="6" width="48.8761061946903" style="1" customWidth="1"/>
+    <col min="7" max="7" width="53.1061946902655" style="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -1342,174 +1375,344 @@
         <v>18</v>
       </c>
     </row>
-    <row r="16" spans="3:7">
-      <c r="C16" s="1">
-        <v>11</v>
-      </c>
-      <c r="D16" s="1">
-        <v>1</v>
-      </c>
-      <c r="E16" s="1">
-        <v>11</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
     <row r="17" spans="3:7">
       <c r="C17" s="1">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D17" s="1">
         <v>1</v>
       </c>
       <c r="E17" s="1">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F17" s="3" t="s">
         <v>19</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="18" spans="3:7">
       <c r="C18" s="1">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D18" s="1">
         <v>1</v>
       </c>
       <c r="E18" s="1">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F18" s="3" t="s">
         <v>19</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="19" spans="3:7">
       <c r="C19" s="1">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D19" s="1">
         <v>1</v>
       </c>
       <c r="E19" s="1">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F19" s="3" t="s">
         <v>19</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="20" spans="3:7">
       <c r="C20" s="1">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D20" s="1">
         <v>1</v>
       </c>
       <c r="E20" s="1">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F20" s="3" t="s">
         <v>19</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21" spans="3:7">
       <c r="C21" s="1">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D21" s="1">
         <v>1</v>
       </c>
       <c r="E21" s="1">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F21" s="3" t="s">
         <v>19</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="22" spans="3:7">
       <c r="C22" s="1">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D22" s="1">
         <v>1</v>
       </c>
       <c r="E22" s="1">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F22" s="3" t="s">
         <v>19</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="23" spans="3:7">
       <c r="C23" s="1">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D23" s="1">
         <v>1</v>
       </c>
       <c r="E23" s="1">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F23" s="3" t="s">
         <v>19</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="24" spans="3:7">
       <c r="C24" s="1">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D24" s="1">
         <v>1</v>
       </c>
       <c r="E24" s="1">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F24" s="3" t="s">
         <v>19</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="25" spans="3:7">
       <c r="C25" s="1">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D25" s="1">
         <v>1</v>
       </c>
       <c r="E25" s="1">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F25" s="3" t="s">
         <v>19</v>
       </c>
       <c r="G25" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="26" spans="3:7">
+      <c r="C26" s="1">
+        <v>20</v>
+      </c>
+      <c r="D26" s="1">
+        <v>1</v>
+      </c>
+      <c r="E26" s="1">
+        <v>20</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G26" s="3" t="s">
         <v>29</v>
+      </c>
+    </row>
+    <row r="28" spans="3:7">
+      <c r="C28" s="1">
+        <v>21</v>
+      </c>
+      <c r="D28" s="1">
+        <v>2</v>
+      </c>
+      <c r="E28" s="1">
+        <v>21</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G28" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="29" spans="3:7">
+      <c r="C29" s="1">
+        <v>22</v>
+      </c>
+      <c r="D29" s="1">
+        <v>2</v>
+      </c>
+      <c r="E29" s="1">
+        <v>22</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="30" spans="3:7">
+      <c r="C30" s="1">
+        <v>23</v>
+      </c>
+      <c r="D30" s="1">
+        <v>2</v>
+      </c>
+      <c r="E30" s="1">
+        <v>23</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G30" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="31" spans="3:7">
+      <c r="C31" s="1">
+        <v>24</v>
+      </c>
+      <c r="D31" s="1">
+        <v>2</v>
+      </c>
+      <c r="E31" s="1">
+        <v>24</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G31" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="32" spans="3:7">
+      <c r="C32" s="1">
+        <v>25</v>
+      </c>
+      <c r="D32" s="1">
+        <v>2</v>
+      </c>
+      <c r="E32" s="1">
+        <v>25</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="33" spans="3:7">
+      <c r="C33" s="1">
+        <v>26</v>
+      </c>
+      <c r="D33" s="1">
+        <v>2</v>
+      </c>
+      <c r="E33" s="1">
+        <v>26</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="34" spans="3:7">
+      <c r="C34" s="1">
+        <v>27</v>
+      </c>
+      <c r="D34" s="1">
+        <v>2</v>
+      </c>
+      <c r="E34" s="1">
+        <v>27</v>
+      </c>
+      <c r="F34" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G34" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="35" spans="3:7">
+      <c r="C35" s="1">
+        <v>28</v>
+      </c>
+      <c r="D35" s="1">
+        <v>2</v>
+      </c>
+      <c r="E35" s="1">
+        <v>28</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="36" spans="3:7">
+      <c r="C36" s="1">
+        <v>29</v>
+      </c>
+      <c r="D36" s="1">
+        <v>2</v>
+      </c>
+      <c r="E36" s="1">
+        <v>29</v>
+      </c>
+      <c r="F36" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G36" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="37" spans="3:7">
+      <c r="C37" s="1">
+        <v>30</v>
+      </c>
+      <c r="D37" s="1">
+        <v>2</v>
+      </c>
+      <c r="E37" s="1">
+        <v>30</v>
+      </c>
+      <c r="F37" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G37" s="3" t="s">
+        <v>40</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/CycleConfig.xlsx
+++ b/Excel/CycleConfig.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27952" windowHeight="12255"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="UnitProto" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="52">
   <si>
     <t>Id</t>
   </si>
@@ -150,6 +150,39 @@
   </si>
   <si>
     <t>51200,102400,153600,51200,60,30,30,30,50,50,50,50</t>
+  </si>
+  <si>
+    <t>2001,2003,2010,2013,31,32,50,51,54,55,94,122</t>
+  </si>
+  <si>
+    <t>100,200,100,100,6,3,3,3,5,5,5,1</t>
+  </si>
+  <si>
+    <t>200,400,200,200,12,6,6,6,10,10,10,2</t>
+  </si>
+  <si>
+    <t>400,800,400,400,18,9,9,9,15,15,15,3</t>
+  </si>
+  <si>
+    <t>800,1600,800,800,24,12,12,12,20,20,20,4</t>
+  </si>
+  <si>
+    <t>1600,3200,1600,1600,30,15,15,15,25,25,25,5</t>
+  </si>
+  <si>
+    <t>3200,6400,3200,3200,36,18,18,18,30,30,30,6</t>
+  </si>
+  <si>
+    <t>6400,12800,6400,6400,42,21,21,21,35,35,35,7</t>
+  </si>
+  <si>
+    <t>12800,25600,12800,12800,48,24,24,24,40,40,40,8</t>
+  </si>
+  <si>
+    <t>25600,51200,25600,25600,54,27,27,27,45,45,45,9</t>
+  </si>
+  <si>
+    <t>51200,102400,51200,51200,60,30,30,30,50,50,50,10</t>
   </si>
 </sst>
 </file>
@@ -1142,19 +1175,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:G37"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.35" outlineLevelCol="6"/>
+  <dimension ref="C3:G48"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="21.1238938053097" style="1" customWidth="1"/>
-    <col min="2" max="2" width="12.7522123893805" style="1" customWidth="1"/>
-    <col min="3" max="4" width="8.87610619469027" style="1" customWidth="1"/>
-    <col min="5" max="5" width="9.50442477876106" style="1" customWidth="1"/>
-    <col min="6" max="6" width="48.8761061946903" style="1" customWidth="1"/>
-    <col min="7" max="7" width="53.1061946902655" style="1" customWidth="1"/>
+    <col min="1" max="1" width="21.1272727272727" style="1" customWidth="1"/>
+    <col min="2" max="2" width="12.7545454545455" style="1" customWidth="1"/>
+    <col min="3" max="4" width="8.87272727272727" style="1" customWidth="1"/>
+    <col min="5" max="5" width="9.5" style="1" customWidth="1"/>
+    <col min="6" max="6" width="48.8727272727273" style="1" customWidth="1"/>
+    <col min="7" max="7" width="53.1090909090909" style="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="3:7">
+    <row r="3" ht="13.5" spans="3:7">
       <c r="C3" s="2" t="s">
         <v>0</v>
       </c>
@@ -1171,7 +1204,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="3:7">
+    <row r="4" ht="13.5" spans="3:7">
       <c r="C4" s="2" t="s">
         <v>0</v>
       </c>
@@ -1188,7 +1221,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="3:7">
+    <row r="5" ht="13.5" spans="3:7">
       <c r="C5" s="2" t="s">
         <v>5</v>
       </c>
@@ -1713,6 +1746,176 @@
       </c>
       <c r="G37" s="3" t="s">
         <v>40</v>
+      </c>
+    </row>
+    <row r="39" spans="3:7">
+      <c r="C39" s="1">
+        <v>31</v>
+      </c>
+      <c r="D39" s="1">
+        <v>3</v>
+      </c>
+      <c r="E39" s="1">
+        <v>31</v>
+      </c>
+      <c r="F39" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="G39" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="40" spans="3:7">
+      <c r="C40" s="1">
+        <v>32</v>
+      </c>
+      <c r="D40" s="1">
+        <v>3</v>
+      </c>
+      <c r="E40" s="1">
+        <v>32</v>
+      </c>
+      <c r="F40" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="G40" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="41" spans="3:7">
+      <c r="C41" s="1">
+        <v>33</v>
+      </c>
+      <c r="D41" s="1">
+        <v>3</v>
+      </c>
+      <c r="E41" s="1">
+        <v>33</v>
+      </c>
+      <c r="F41" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="G41" s="3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="42" spans="3:7">
+      <c r="C42" s="1">
+        <v>34</v>
+      </c>
+      <c r="D42" s="1">
+        <v>3</v>
+      </c>
+      <c r="E42" s="1">
+        <v>34</v>
+      </c>
+      <c r="F42" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="G42" s="3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="43" spans="3:7">
+      <c r="C43" s="1">
+        <v>35</v>
+      </c>
+      <c r="D43" s="1">
+        <v>3</v>
+      </c>
+      <c r="E43" s="1">
+        <v>35</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="44" spans="3:7">
+      <c r="C44" s="1">
+        <v>36</v>
+      </c>
+      <c r="D44" s="1">
+        <v>3</v>
+      </c>
+      <c r="E44" s="1">
+        <v>36</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="45" spans="3:7">
+      <c r="C45" s="1">
+        <v>37</v>
+      </c>
+      <c r="D45" s="1">
+        <v>3</v>
+      </c>
+      <c r="E45" s="1">
+        <v>37</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="46" spans="3:7">
+      <c r="C46" s="1">
+        <v>38</v>
+      </c>
+      <c r="D46" s="1">
+        <v>3</v>
+      </c>
+      <c r="E46" s="1">
+        <v>38</v>
+      </c>
+      <c r="F46" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="G46" s="3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="47" spans="3:7">
+      <c r="C47" s="1">
+        <v>39</v>
+      </c>
+      <c r="D47" s="1">
+        <v>3</v>
+      </c>
+      <c r="E47" s="1">
+        <v>39</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="48" spans="3:7">
+      <c r="C48" s="1">
+        <v>40</v>
+      </c>
+      <c r="D48" s="1">
+        <v>3</v>
+      </c>
+      <c r="E48" s="1">
+        <v>40</v>
+      </c>
+      <c r="F48" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>51</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/CycleConfig.xlsx
+++ b/Excel/CycleConfig.xlsx
@@ -1,8 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\WrittenLegend\Excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView windowHeight="17680"/>
   </bookViews>
@@ -27,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="63">
   <si>
     <t>Id</t>
   </si>
@@ -183,6 +188,39 @@
   </si>
   <si>
     <t>51200,102400,51200,51200,60,30,30,30,50,50,50,10</t>
+  </si>
+  <si>
+    <t>2001,2003,2010,2013,31,32,50,51,52,53,94,123</t>
+  </si>
+  <si>
+    <t>200,400,200,200,15,10,5,5,5,5,10,1</t>
+  </si>
+  <si>
+    <t>400,800,400,400,30,20,10,10,10,10,20,2</t>
+  </si>
+  <si>
+    <t>800,1600,800,800,45,30,15,15,15,15,30,3</t>
+  </si>
+  <si>
+    <t>1600,3200,1600,1600,60,40,20,20,20,20,40,4</t>
+  </si>
+  <si>
+    <t>3200,6400,3200,3200,75,50,25,25,25,25,50,5</t>
+  </si>
+  <si>
+    <t>6400,12800,6400,6400,90,60,30,30,30,30,60,6</t>
+  </si>
+  <si>
+    <t>12800,25600,12800,12800,105,70,35,35,35,35,70,7</t>
+  </si>
+  <si>
+    <t>25600,51200,25600,25600,120,80,40,40,40,40,80,8</t>
+  </si>
+  <si>
+    <t>51200,102400,51200,51200,135,90,45,45,45,45,90,9</t>
+  </si>
+  <si>
+    <t>102400,204800,102400,102400,150,100,50,50,50,50,100,10</t>
   </si>
 </sst>
 </file>
@@ -1175,7 +1213,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:G48"/>
+  <dimension ref="C3:G59"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="21.1272727272727" style="1" customWidth="1"/>
@@ -1918,6 +1956,176 @@
         <v>51</v>
       </c>
     </row>
+    <row r="50" spans="3:7">
+      <c r="C50" s="1">
+        <v>51</v>
+      </c>
+      <c r="D50" s="1">
+        <v>4</v>
+      </c>
+      <c r="E50" s="1">
+        <v>41</v>
+      </c>
+      <c r="F50" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="G50" s="3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="51" spans="3:7">
+      <c r="C51" s="1">
+        <v>52</v>
+      </c>
+      <c r="D51" s="1">
+        <v>4</v>
+      </c>
+      <c r="E51" s="1">
+        <v>42</v>
+      </c>
+      <c r="F51" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="G51" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="52" spans="3:7">
+      <c r="C52" s="1">
+        <v>53</v>
+      </c>
+      <c r="D52" s="1">
+        <v>4</v>
+      </c>
+      <c r="E52" s="1">
+        <v>43</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="53" spans="3:7">
+      <c r="C53" s="1">
+        <v>54</v>
+      </c>
+      <c r="D53" s="1">
+        <v>4</v>
+      </c>
+      <c r="E53" s="1">
+        <v>44</v>
+      </c>
+      <c r="F53" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="G53" s="3" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="54" spans="3:7">
+      <c r="C54" s="1">
+        <v>55</v>
+      </c>
+      <c r="D54" s="1">
+        <v>4</v>
+      </c>
+      <c r="E54" s="1">
+        <v>45</v>
+      </c>
+      <c r="F54" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="G54" s="3" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="55" spans="3:7">
+      <c r="C55" s="1">
+        <v>56</v>
+      </c>
+      <c r="D55" s="1">
+        <v>4</v>
+      </c>
+      <c r="E55" s="1">
+        <v>46</v>
+      </c>
+      <c r="F55" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="G55" s="3" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="56" spans="3:7">
+      <c r="C56" s="1">
+        <v>57</v>
+      </c>
+      <c r="D56" s="1">
+        <v>4</v>
+      </c>
+      <c r="E56" s="1">
+        <v>47</v>
+      </c>
+      <c r="F56" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="G56" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="57" spans="3:7">
+      <c r="C57" s="1">
+        <v>58</v>
+      </c>
+      <c r="D57" s="1">
+        <v>4</v>
+      </c>
+      <c r="E57" s="1">
+        <v>48</v>
+      </c>
+      <c r="F57" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="G57" s="3" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="58" spans="3:7">
+      <c r="C58" s="1">
+        <v>59</v>
+      </c>
+      <c r="D58" s="1">
+        <v>4</v>
+      </c>
+      <c r="E58" s="1">
+        <v>49</v>
+      </c>
+      <c r="F58" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="G58" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="59" spans="3:7">
+      <c r="C59" s="1">
+        <v>60</v>
+      </c>
+      <c r="D59" s="1">
+        <v>4</v>
+      </c>
+      <c r="E59" s="1">
+        <v>50</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>62</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
